--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/160.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/160.xlsx
@@ -426,13 +426,13 @@
         <v>-7.089934493181977</v>
       </c>
       <c r="E2">
-        <v>-7.225698601982532</v>
+        <v>-10.09704547365604</v>
       </c>
       <c r="F2">
-        <v>-3.400663058693019</v>
+        <v>-3.565092909069435</v>
       </c>
       <c r="G2">
-        <v>-6.617990248040411</v>
+        <v>-7.265042994782043</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-6.969277909809544</v>
       </c>
       <c r="E3">
-        <v>-8.20063829956789</v>
+        <v>-10.08548880798846</v>
       </c>
       <c r="F3">
-        <v>-3.384496588708213</v>
+        <v>-3.927776608911266</v>
       </c>
       <c r="G3">
-        <v>-5.783971131422899</v>
+        <v>-6.935445080892204</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-6.800068075113813</v>
       </c>
       <c r="E4">
-        <v>-8.342710114610533</v>
+        <v>-10.19275930028216</v>
       </c>
       <c r="F4">
-        <v>-3.559907855902286</v>
+        <v>-3.608772310070213</v>
       </c>
       <c r="G4">
-        <v>-6.001473973353017</v>
+        <v>-7.59297239372009</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-6.585211891297942</v>
       </c>
       <c r="E5">
-        <v>-9.154787772984035</v>
+        <v>-11.076477417457</v>
       </c>
       <c r="F5">
-        <v>-3.558659103787963</v>
+        <v>-3.904153259623613</v>
       </c>
       <c r="G5">
-        <v>-5.914207992937828</v>
+        <v>-7.324526877031667</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-6.30902964193728</v>
       </c>
       <c r="E6">
-        <v>-9.875539696044848</v>
+        <v>-11.51357478562536</v>
       </c>
       <c r="F6">
-        <v>-3.238505826305259</v>
+        <v>-3.683325266039525</v>
       </c>
       <c r="G6">
-        <v>-4.951961515947725</v>
+        <v>-7.211167176675944</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-5.961447879183224</v>
       </c>
       <c r="E7">
-        <v>-10.93037978902154</v>
+        <v>-12.17492671512757</v>
       </c>
       <c r="F7">
-        <v>-3.28406983734541</v>
+        <v>-3.656437898860152</v>
       </c>
       <c r="G7">
-        <v>-5.517290135506909</v>
+        <v>-6.240200722735401</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-5.534211713495353</v>
       </c>
       <c r="E8">
-        <v>-11.08300294850206</v>
+        <v>-12.38515659245965</v>
       </c>
       <c r="F8">
-        <v>-3.333627162851341</v>
+        <v>-3.745532442545029</v>
       </c>
       <c r="G8">
-        <v>-4.891269284576267</v>
+        <v>-6.289061064349505</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-5.02390817257981</v>
       </c>
       <c r="E9">
-        <v>-11.72325218912852</v>
+        <v>-14.33768967339887</v>
       </c>
       <c r="F9">
-        <v>-3.29967884284798</v>
+        <v>-3.714544068897625</v>
       </c>
       <c r="G9">
-        <v>-3.623336964126481</v>
+        <v>-5.392608369406878</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-4.440752528210937</v>
       </c>
       <c r="E10">
-        <v>-13.5294114047178</v>
+        <v>-13.24546249901485</v>
       </c>
       <c r="F10">
-        <v>-3.002212152603947</v>
+        <v>-3.75802629851193</v>
       </c>
       <c r="G10">
-        <v>-3.606529324423601</v>
+        <v>-6.050668680066586</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-3.79891468955153</v>
       </c>
       <c r="E11">
-        <v>-13.34217711839666</v>
+        <v>-14.82005819622191</v>
       </c>
       <c r="F11">
-        <v>-3.156768388450556</v>
+        <v>-3.856017310176789</v>
       </c>
       <c r="G11">
-        <v>-3.092898184005676</v>
+        <v>-5.14662821474795</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-3.130037164190359</v>
       </c>
       <c r="E12">
-        <v>-14.23821721334638</v>
+        <v>-15.12757780913478</v>
       </c>
       <c r="F12">
-        <v>-2.920874600492892</v>
+        <v>-3.432411611179834</v>
       </c>
       <c r="G12">
-        <v>-2.610948964398577</v>
+        <v>-4.255584951216492</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-2.461843550497521</v>
       </c>
       <c r="E13">
-        <v>-14.25821495456425</v>
+        <v>-16.01604629554368</v>
       </c>
       <c r="F13">
-        <v>-2.963739976653134</v>
+        <v>-3.239996885424645</v>
       </c>
       <c r="G13">
-        <v>-1.969788988716847</v>
+        <v>-4.7868248833578</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-1.83468166945069</v>
       </c>
       <c r="E14">
-        <v>-14.539089026416</v>
+        <v>-16.5683072862011</v>
       </c>
       <c r="F14">
-        <v>-2.752524286122806</v>
+        <v>-3.176810186810442</v>
       </c>
       <c r="G14">
-        <v>-0.7456949122980903</v>
+        <v>-2.971987129274874</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-1.275722297230641</v>
       </c>
       <c r="E15">
-        <v>-16.37782155554245</v>
+        <v>-16.82296149354844</v>
       </c>
       <c r="F15">
-        <v>-2.553141254339684</v>
+        <v>-2.799717930549944</v>
       </c>
       <c r="G15">
-        <v>-1.141013776233541</v>
+        <v>-2.234248608575987</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-0.815816387836098</v>
       </c>
       <c r="E16">
-        <v>-15.75119849320508</v>
+        <v>-17.57445722664732</v>
       </c>
       <c r="F16">
-        <v>-2.396973597724115</v>
+        <v>-2.839638405560426</v>
       </c>
       <c r="G16">
-        <v>-0.3172705929699274</v>
+        <v>-2.596008472379846</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-0.4699962709051475</v>
       </c>
       <c r="E17">
-        <v>-18.40494766033601</v>
+        <v>-18.79340468918798</v>
       </c>
       <c r="F17">
-        <v>-2.180500795407486</v>
+        <v>-2.661715380784466</v>
       </c>
       <c r="G17">
-        <v>0.2621212240400801</v>
+        <v>-1.774576049902643</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-0.2516374764997111</v>
       </c>
       <c r="E18">
-        <v>-19.31714987901911</v>
+        <v>-20.82902621121993</v>
       </c>
       <c r="F18">
-        <v>-1.984812549525083</v>
+        <v>-1.862514027617103</v>
       </c>
       <c r="G18">
-        <v>0.5311295334701782</v>
+        <v>-1.175595734936768</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-0.1601512033795328</v>
       </c>
       <c r="E19">
-        <v>-19.40554116317482</v>
+        <v>-20.89027382217368</v>
       </c>
       <c r="F19">
-        <v>-1.813250479558486</v>
+        <v>-2.31422971476015</v>
       </c>
       <c r="G19">
-        <v>1.227257807285966</v>
+        <v>-1.96155566196068</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-0.1923133933886854</v>
       </c>
       <c r="E20">
-        <v>-19.70233734963754</v>
+        <v>-20.79715028267994</v>
       </c>
       <c r="F20">
-        <v>-1.441450968467386</v>
+        <v>-1.88227788558883</v>
       </c>
       <c r="G20">
-        <v>0.6212856201411505</v>
+        <v>-0.836480002621524</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-0.3347964313730766</v>
       </c>
       <c r="E21">
-        <v>-20.80758388679361</v>
+        <v>-21.9199808844078</v>
       </c>
       <c r="F21">
-        <v>-1.307393430137268</v>
+        <v>-1.548762089444605</v>
       </c>
       <c r="G21">
-        <v>0.7585011116528626</v>
+        <v>-0.6843769878197093</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-0.5746615063830711</v>
       </c>
       <c r="E22">
-        <v>-22.09516490139453</v>
+        <v>-23.13892834694846</v>
       </c>
       <c r="F22">
-        <v>-0.9882252177339673</v>
+        <v>-1.062654644641875</v>
       </c>
       <c r="G22">
-        <v>1.084632884363085</v>
+        <v>0.08614586535458092</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-0.8938846543313986</v>
       </c>
       <c r="E23">
-        <v>-22.66377821169365</v>
+        <v>-22.43187505776085</v>
       </c>
       <c r="F23">
-        <v>-0.7227604729232185</v>
+        <v>-1.412152409031756</v>
       </c>
       <c r="G23">
-        <v>0.4826896311395623</v>
+        <v>-2.005910351095835</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-1.278315735683734</v>
       </c>
       <c r="E24">
-        <v>-22.40323245966233</v>
+        <v>-23.56027568251814</v>
       </c>
       <c r="F24">
-        <v>-1.010808864088134</v>
+        <v>-1.036685826893457</v>
       </c>
       <c r="G24">
-        <v>0.9954037504431088</v>
+        <v>-1.210267078369555</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-1.71042783770529</v>
       </c>
       <c r="E25">
-        <v>-22.94667198295281</v>
+        <v>-24.66345723552672</v>
       </c>
       <c r="F25">
-        <v>-0.8500642973769454</v>
+        <v>-1.160073146618302</v>
       </c>
       <c r="G25">
-        <v>0.8848414610680689</v>
+        <v>-1.044931813047274</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-2.178055478912232</v>
       </c>
       <c r="E26">
-        <v>-22.42513668843743</v>
+        <v>-23.265001063322</v>
       </c>
       <c r="F26">
-        <v>-0.8337259953003143</v>
+        <v>-0.9822332664029022</v>
       </c>
       <c r="G26">
-        <v>0.07487345779336252</v>
+        <v>-1.139510788558712</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-2.664613594463293</v>
       </c>
       <c r="E27">
-        <v>-23.11772150317054</v>
+        <v>-24.42367453682057</v>
       </c>
       <c r="F27">
-        <v>-0.6344625333138076</v>
+        <v>-0.7066423059688336</v>
       </c>
       <c r="G27">
-        <v>0.4313728647353196</v>
+        <v>-0.9775291058677122</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-3.160838631346762</v>
       </c>
       <c r="E28">
-        <v>-22.46118334153849</v>
+        <v>-25.03404037747041</v>
       </c>
       <c r="F28">
-        <v>-0.6186729853368763</v>
+        <v>-1.336744251868107</v>
       </c>
       <c r="G28">
-        <v>0.003971503978791511</v>
+        <v>-1.089226912362722</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-3.650769211795554</v>
       </c>
       <c r="E29">
-        <v>-22.4682749318345</v>
+        <v>-25.13598991280509</v>
       </c>
       <c r="F29">
-        <v>-0.4695781593396605</v>
+        <v>-1.02376674588826</v>
       </c>
       <c r="G29">
-        <v>0.5743255316665887</v>
+        <v>-1.531148325854494</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-4.125614355408668</v>
       </c>
       <c r="E30">
-        <v>-22.19261766203959</v>
+        <v>-23.06599274458092</v>
       </c>
       <c r="F30">
-        <v>-0.7382221937756539</v>
+        <v>-1.381221840650266</v>
       </c>
       <c r="G30">
-        <v>0.1862170359156703</v>
+        <v>-2.19598863377863</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-4.567203817184818</v>
       </c>
       <c r="E31">
-        <v>-21.93655057080186</v>
+        <v>-23.63130479732845</v>
       </c>
       <c r="F31">
-        <v>-0.7772740060915175</v>
+        <v>-1.494899459407552</v>
       </c>
       <c r="G31">
-        <v>0.02015345057474907</v>
+        <v>-0.9883413475989719</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-4.965986858927412</v>
       </c>
       <c r="E32">
-        <v>-20.94931606628568</v>
+        <v>-22.52953612821027</v>
       </c>
       <c r="F32">
-        <v>-0.9191075404664436</v>
+        <v>-0.9934696598729451</v>
       </c>
       <c r="G32">
-        <v>-0.5018831649673852</v>
+        <v>-1.181905634734619</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-5.304480552599808</v>
       </c>
       <c r="E33">
-        <v>-20.47148960289233</v>
+        <v>-22.57872894135559</v>
       </c>
       <c r="F33">
-        <v>-0.9850095028726675</v>
+        <v>-1.129650947835668</v>
       </c>
       <c r="G33">
-        <v>-0.2461998013328535</v>
+        <v>-0.8198875483786968</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-5.577361737962521</v>
       </c>
       <c r="E34">
-        <v>-20.51579166410938</v>
+        <v>-22.97620216195683</v>
       </c>
       <c r="F34">
-        <v>-1.08412415388453</v>
+        <v>-1.915422474840104</v>
       </c>
       <c r="G34">
-        <v>0.1005334962682535</v>
+        <v>-1.47047595775627</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-5.776218281610136</v>
       </c>
       <c r="E35">
-        <v>-20.42918459871268</v>
+        <v>-21.2508988497745</v>
       </c>
       <c r="F35">
-        <v>-1.06434049958886</v>
+        <v>-1.535503303520546</v>
       </c>
       <c r="G35">
-        <v>0.0446349348376595</v>
+        <v>-1.283612214792108</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-5.90340644890906</v>
       </c>
       <c r="E36">
-        <v>-19.03167487757557</v>
+        <v>-21.01795867529395</v>
       </c>
       <c r="F36">
-        <v>-0.8209391537390562</v>
+        <v>-1.258868680888203</v>
       </c>
       <c r="G36">
-        <v>0.1206980291479543</v>
+        <v>-0.9916187876828504</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-5.961910503316306</v>
       </c>
       <c r="E37">
-        <v>-19.12022012984755</v>
+        <v>-21.82731019231483</v>
       </c>
       <c r="F37">
-        <v>-1.248295860196729</v>
+        <v>-1.24028072455869</v>
       </c>
       <c r="G37">
-        <v>0.2985736409729952</v>
+        <v>-1.221125667738365</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-5.96093611395572</v>
       </c>
       <c r="E38">
-        <v>-18.34558842304347</v>
+        <v>-20.85788164759681</v>
       </c>
       <c r="F38">
-        <v>-1.226830310218863</v>
+        <v>-1.261480211942763</v>
       </c>
       <c r="G38">
-        <v>0.6367028307175364</v>
+        <v>-1.803079846995768</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-5.913396796534275</v>
       </c>
       <c r="E39">
-        <v>-18.77443491156985</v>
+        <v>-21.11959121744809</v>
       </c>
       <c r="F39">
-        <v>-1.094133967123065</v>
+        <v>-1.766742579792733</v>
       </c>
       <c r="G39">
-        <v>0.525475121689103</v>
+        <v>-0.8304382570123541</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-5.833727112274141</v>
       </c>
       <c r="E40">
-        <v>-17.71297418959394</v>
+        <v>-20.05776821755157</v>
       </c>
       <c r="F40">
-        <v>-0.7258605772526913</v>
+        <v>-1.23815222380834</v>
       </c>
       <c r="G40">
-        <v>0.3329172403973945</v>
+        <v>-1.26398067974423</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-5.740880097222255</v>
       </c>
       <c r="E41">
-        <v>-17.35772446064022</v>
+        <v>-20.01870560076141</v>
       </c>
       <c r="F41">
-        <v>-0.7460947958813035</v>
+        <v>-1.124039877777266</v>
       </c>
       <c r="G41">
-        <v>-0.1622807824578682</v>
+        <v>-1.492557296503209</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-5.650245816512337</v>
       </c>
       <c r="E42">
-        <v>-16.70516229918691</v>
+        <v>-18.41832930102868</v>
       </c>
       <c r="F42">
-        <v>-0.8224777240359057</v>
+        <v>-1.287596314341317</v>
       </c>
       <c r="G42">
-        <v>0.6883043040381563</v>
+        <v>-1.360135474932362</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-5.580365248643744</v>
       </c>
       <c r="E43">
-        <v>-17.00050031701915</v>
+        <v>-18.77443038309584</v>
       </c>
       <c r="F43">
-        <v>-0.9918083523676491</v>
+        <v>-1.589941610657862</v>
       </c>
       <c r="G43">
-        <v>0.2379774154221754</v>
+        <v>-1.800954476759556</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-5.541632670508328</v>
       </c>
       <c r="E44">
-        <v>-16.40131980716826</v>
+        <v>-16.66205122663388</v>
       </c>
       <c r="F44">
-        <v>-1.195440467121895</v>
+        <v>-1.463544457840724</v>
       </c>
       <c r="G44">
-        <v>0.9967279686588173</v>
+        <v>-1.061948017119128</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-5.546862306245324</v>
       </c>
       <c r="E45">
-        <v>-15.23576758165204</v>
+        <v>-16.85022743554862</v>
       </c>
       <c r="F45">
-        <v>-0.826920810981671</v>
+        <v>-1.19624103046215</v>
       </c>
       <c r="G45">
-        <v>0.07253952318817633</v>
+        <v>-2.274216824871608</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-5.59832035221467</v>
       </c>
       <c r="E46">
-        <v>-14.76254204785048</v>
+        <v>-17.02767116106518</v>
       </c>
       <c r="F46">
-        <v>-1.183181791483437</v>
+        <v>-1.483111144425979</v>
       </c>
       <c r="G46">
-        <v>-0.1382561534793772</v>
+        <v>-2.059925212114584</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-5.70080265414519</v>
       </c>
       <c r="E47">
-        <v>-14.02302412850188</v>
+        <v>-16.06725427962241</v>
       </c>
       <c r="F47">
-        <v>-1.153559364188099</v>
+        <v>-1.49465715240249</v>
       </c>
       <c r="G47">
-        <v>-0.3839118746754564</v>
+        <v>-2.747300403524539</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-5.84835189839037</v>
       </c>
       <c r="E48">
-        <v>-14.30569147606067</v>
+        <v>-16.320287293275</v>
       </c>
       <c r="F48">
-        <v>-1.225497621691021</v>
+        <v>-1.038910933704649</v>
       </c>
       <c r="G48">
-        <v>0.1503042379056565</v>
+        <v>-1.624982428619596</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-6.03769342555285</v>
       </c>
       <c r="E49">
-        <v>-13.67918615404749</v>
+        <v>-15.15305500390194</v>
       </c>
       <c r="F49">
-        <v>-0.8956726521827283</v>
+        <v>-1.31690754342427</v>
       </c>
       <c r="G49">
-        <v>0.04186069767575025</v>
+        <v>-2.547005777307554</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-6.255961812624855</v>
       </c>
       <c r="E50">
-        <v>-13.26010758395565</v>
+        <v>-14.63161480734072</v>
       </c>
       <c r="F50">
-        <v>-1.187218657861892</v>
+        <v>-1.198963420930791</v>
       </c>
       <c r="G50">
-        <v>-0.856048637304156</v>
+        <v>-3.138272521166927</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-6.493327815321439</v>
       </c>
       <c r="E51">
-        <v>-12.87525069193978</v>
+        <v>-13.77049830393815</v>
       </c>
       <c r="F51">
-        <v>-0.9888761208652129</v>
+        <v>-1.191631654395264</v>
       </c>
       <c r="G51">
-        <v>-0.97885663462896</v>
+        <v>-2.462911299518987</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-6.733965955387221</v>
       </c>
       <c r="E52">
-        <v>-12.18805928974981</v>
+        <v>-14.1009048244858</v>
       </c>
       <c r="F52">
-        <v>-1.098246851385461</v>
+        <v>-1.425655085666793</v>
       </c>
       <c r="G52">
-        <v>-0.6902532061519157</v>
+        <v>-2.585027392826083</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-6.965886550891772</v>
       </c>
       <c r="E53">
-        <v>-12.12852797044497</v>
+        <v>-13.6372751271065</v>
       </c>
       <c r="F53">
-        <v>-1.318582312429847</v>
+        <v>-1.492479556768761</v>
       </c>
       <c r="G53">
-        <v>-0.9892020894391824</v>
+        <v>-3.155510531789912</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-7.175265738675264</v>
       </c>
       <c r="E54">
-        <v>-10.97450071127828</v>
+        <v>-13.52222018799362</v>
       </c>
       <c r="F54">
-        <v>-1.506954628835877</v>
+        <v>-1.082844519504855</v>
       </c>
       <c r="G54">
-        <v>-1.370904679571611</v>
+        <v>-3.336607304424664</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-7.352025408290862</v>
       </c>
       <c r="E55">
-        <v>-10.59598368287314</v>
+        <v>-12.44419883657166</v>
       </c>
       <c r="F55">
-        <v>-1.054842223361012</v>
+        <v>-1.675342160294976</v>
       </c>
       <c r="G55">
-        <v>-1.117661187999522</v>
+        <v>-2.190208421267062</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-7.487570510762552</v>
       </c>
       <c r="E56">
-        <v>-10.40388581546777</v>
+        <v>-12.43420902291074</v>
       </c>
       <c r="F56">
-        <v>-1.40543512039142</v>
+        <v>-1.591410497894432</v>
       </c>
       <c r="G56">
-        <v>-1.299416759196589</v>
+        <v>-2.556973829926299</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-7.574341489045229</v>
       </c>
       <c r="E57">
-        <v>-10.22687229498194</v>
+        <v>-12.68367812751929</v>
       </c>
       <c r="F57">
-        <v>-1.135275479394351</v>
+        <v>-1.418670942579705</v>
       </c>
       <c r="G57">
-        <v>-1.972712200428024</v>
+        <v>-2.671369731035815</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-7.609743910253319</v>
       </c>
       <c r="E58">
-        <v>-9.741207043081316</v>
+        <v>-11.38970290761955</v>
       </c>
       <c r="F58">
-        <v>-1.518758780876605</v>
+        <v>-1.522654697428586</v>
       </c>
       <c r="G58">
-        <v>-2.173331260107858</v>
+        <v>-3.933551633883887</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-7.590675408135572</v>
       </c>
       <c r="E59">
-        <v>-9.8269219990985</v>
+        <v>-11.21659293172833</v>
       </c>
       <c r="F59">
-        <v>-1.464551694802944</v>
+        <v>-1.128692805756827</v>
       </c>
       <c r="G59">
-        <v>-2.001987354631799</v>
+        <v>-3.064649298919075</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-7.521189288983892</v>
       </c>
       <c r="E60">
-        <v>-9.780767792012323</v>
+        <v>-10.7917903704908</v>
       </c>
       <c r="F60">
-        <v>-1.587946141204408</v>
+        <v>-1.973696517704614</v>
       </c>
       <c r="G60">
-        <v>-3.005072721394351</v>
+        <v>-4.462454320874469</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-7.402267210481066</v>
       </c>
       <c r="E61">
-        <v>-9.400647683808474</v>
+        <v>-11.30611633438597</v>
       </c>
       <c r="F61">
-        <v>-1.797824392089148</v>
+        <v>-1.781966744757853</v>
       </c>
       <c r="G61">
-        <v>-1.967584165387693</v>
+        <v>-4.462202719413485</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-7.24204437508102</v>
       </c>
       <c r="E62">
-        <v>-8.864974493441148</v>
+        <v>-10.69052010625727</v>
       </c>
       <c r="F62">
-        <v>-1.757226090946858</v>
+        <v>-1.867087770300892</v>
       </c>
       <c r="G62">
-        <v>-2.80879709746204</v>
+        <v>-5.053267519994963</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-7.045415595938982</v>
       </c>
       <c r="E63">
-        <v>-9.117436919368769</v>
+        <v>-10.36208800037697</v>
       </c>
       <c r="F63">
-        <v>-1.932868579204585</v>
+        <v>-1.765291905174191</v>
       </c>
       <c r="G63">
-        <v>-2.14956485368143</v>
+        <v>-3.86176907495587</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-6.824109491487204</v>
       </c>
       <c r="E64">
-        <v>-9.040448332764367</v>
+        <v>-10.14301854178191</v>
       </c>
       <c r="F64">
-        <v>-2.203208762676014</v>
+        <v>-1.632317621690233</v>
       </c>
       <c r="G64">
-        <v>-2.372788318303408</v>
+        <v>-4.562359964158595</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-6.584322953269045</v>
       </c>
       <c r="E65">
-        <v>-8.700812782189089</v>
+        <v>-10.83304929717468</v>
       </c>
       <c r="F65">
-        <v>-1.894303756457719</v>
+        <v>-1.883459330201747</v>
       </c>
       <c r="G65">
-        <v>-2.767875444051109</v>
+        <v>-4.353365224264405</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-6.334718247830203</v>
       </c>
       <c r="E66">
-        <v>-8.834656359959794</v>
+        <v>-10.50967096828694</v>
       </c>
       <c r="F66">
-        <v>-2.259002722076946</v>
+        <v>-2.084991450912121</v>
       </c>
       <c r="G66">
-        <v>-2.794902737833719</v>
+        <v>-4.896999838904745</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-6.078501183182553</v>
       </c>
       <c r="E67">
-        <v>-9.041901972920828</v>
+        <v>-10.14757871510763</v>
       </c>
       <c r="F67">
-        <v>-1.857332141861785</v>
+        <v>-1.879994973511724</v>
       </c>
       <c r="G67">
-        <v>-3.193932723318694</v>
+        <v>-5.213031137174651</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-5.818904323233641</v>
       </c>
       <c r="E68">
-        <v>-9.207766390399771</v>
+        <v>-9.332177156812499</v>
       </c>
       <c r="F68">
-        <v>-1.889145626291133</v>
+        <v>-1.970623336375704</v>
       </c>
       <c r="G68">
-        <v>-3.22674354015841</v>
+        <v>-5.384586917565223</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-5.556621952387778</v>
       </c>
       <c r="E69">
-        <v>-8.899449766061542</v>
+        <v>-9.571348511527608</v>
       </c>
       <c r="F69">
-        <v>-2.127445063534349</v>
+        <v>-2.382797846075016</v>
       </c>
       <c r="G69">
-        <v>-3.024260643339967</v>
+        <v>-6.335875488820339</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-5.290217650973515</v>
       </c>
       <c r="E70">
-        <v>-9.799615300832247</v>
+        <v>-10.12484577558913</v>
       </c>
       <c r="F70">
-        <v>-2.135144249842257</v>
+        <v>-2.399024496884609</v>
       </c>
       <c r="G70">
-        <v>-3.286495576596716</v>
+        <v>-4.652578951194814</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-5.020541889190391</v>
       </c>
       <c r="E71">
-        <v>-7.981029952565916</v>
+        <v>-9.729337912707212</v>
       </c>
       <c r="F71">
-        <v>-2.585897043788718</v>
+        <v>-2.694463251703922</v>
       </c>
       <c r="G71">
-        <v>-3.002301794777981</v>
+        <v>-5.437188175638703</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-4.744286290010535</v>
       </c>
       <c r="E72">
-        <v>-10.00339663117741</v>
+        <v>-10.76427083394619</v>
       </c>
       <c r="F72">
-        <v>-2.513726773369184</v>
+        <v>-2.388389119809475</v>
       </c>
       <c r="G72">
-        <v>-3.223442926255757</v>
+        <v>-4.709209143189587</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-4.465244415501775</v>
       </c>
       <c r="E73">
-        <v>-8.880606785715626</v>
+        <v>-9.928414158558407</v>
       </c>
       <c r="F73">
-        <v>-2.701990605920006</v>
+        <v>-2.393626435271834</v>
       </c>
       <c r="G73">
-        <v>-2.974129052238783</v>
+        <v>-4.79041351472237</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-4.180889563216452</v>
       </c>
       <c r="E74">
-        <v>-10.29827727313488</v>
+        <v>-10.67489687093081</v>
       </c>
       <c r="F74">
-        <v>-2.584419446169612</v>
+        <v>-2.591038545043192</v>
       </c>
       <c r="G74">
-        <v>-3.656538425339831</v>
+        <v>-4.758824289186644</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-3.898113793669974</v>
       </c>
       <c r="E75">
-        <v>-9.968690406382628</v>
+        <v>-10.71410892736322</v>
       </c>
       <c r="F75">
-        <v>-2.409100825771592</v>
+        <v>-2.727921414726454</v>
       </c>
       <c r="G75">
-        <v>-2.916131604936291</v>
+        <v>-4.406870261270107</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.616815061980251</v>
       </c>
       <c r="E76">
-        <v>-10.28974562810443</v>
+        <v>-12.27281420927737</v>
       </c>
       <c r="F76">
-        <v>-2.69438089899632</v>
+        <v>-2.516899728170767</v>
       </c>
       <c r="G76">
-        <v>-2.939927806272572</v>
+        <v>-4.888236824862294</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.345561308758724</v>
       </c>
       <c r="E77">
-        <v>-10.913524808765</v>
+        <v>-11.71398693130882</v>
       </c>
       <c r="F77">
-        <v>-2.781836307058717</v>
+        <v>-2.075707766835815</v>
       </c>
       <c r="G77">
-        <v>-2.981382457515326</v>
+        <v>-4.259974734601565</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-3.086776123785458</v>
       </c>
       <c r="E78">
-        <v>-11.73354088207394</v>
+        <v>-12.40104700775257</v>
       </c>
       <c r="F78">
-        <v>-2.37349357382181</v>
+        <v>-2.806809765639282</v>
       </c>
       <c r="G78">
-        <v>-2.55415655567238</v>
+        <v>-4.543956641505787</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-2.849866386218358</v>
       </c>
       <c r="E79">
-        <v>-11.5866869984792</v>
+        <v>-12.0095196735234</v>
       </c>
       <c r="F79">
-        <v>-2.892645834403142</v>
+        <v>-2.374108051717</v>
       </c>
       <c r="G79">
-        <v>-2.846921339892288</v>
+        <v>-3.95071019141393</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-2.638879499090155</v>
       </c>
       <c r="E80">
-        <v>-13.2441356561306</v>
+        <v>-12.81909308577066</v>
       </c>
       <c r="F80">
-        <v>-2.426268989747914</v>
+        <v>-2.636115566514345</v>
       </c>
       <c r="G80">
-        <v>-2.865778207283976</v>
+        <v>-4.4474178230351</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-2.463028935079635</v>
       </c>
       <c r="E81">
-        <v>-13.40789433319597</v>
+        <v>-13.15502887308167</v>
       </c>
       <c r="F81">
-        <v>-2.740914929909677</v>
+        <v>-2.671081417568375</v>
       </c>
       <c r="G81">
-        <v>-2.098162013093166</v>
+        <v>-3.470406312939848</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-2.326431421252834</v>
       </c>
       <c r="E82">
-        <v>-14.30774740326015</v>
+        <v>-15.04779515406765</v>
       </c>
       <c r="F82">
-        <v>-2.673735708682651</v>
+        <v>-2.781339023401269</v>
       </c>
       <c r="G82">
-        <v>-2.084618571292008</v>
+        <v>-3.612173804568058</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-2.236817581095137</v>
       </c>
       <c r="E83">
-        <v>-15.2641429997841</v>
+        <v>-15.73074790458644</v>
       </c>
       <c r="F83">
-        <v>-2.364115659243535</v>
+        <v>-2.712610937788943</v>
       </c>
       <c r="G83">
-        <v>-3.238625088098854</v>
+        <v>-4.102746995304959</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-2.196604685307142</v>
       </c>
       <c r="E84">
-        <v>-16.36139678031664</v>
+        <v>-15.66815533685242</v>
       </c>
       <c r="F84">
-        <v>-2.457821162701214</v>
+        <v>-2.801486138204532</v>
       </c>
       <c r="G84">
-        <v>-1.891732945991911</v>
+        <v>-3.289137391937054</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-2.210146623854529</v>
       </c>
       <c r="E85">
-        <v>-16.81029082327497</v>
+        <v>-17.91044735564643</v>
       </c>
       <c r="F85">
-        <v>-2.987807555450067</v>
+        <v>-2.587696133708657</v>
       </c>
       <c r="G85">
-        <v>-2.403069878351121</v>
+        <v>-3.314221395488112</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-2.276073037326494</v>
       </c>
       <c r="E86">
-        <v>-19.05746453704925</v>
+        <v>-18.59385748203999</v>
       </c>
       <c r="F86">
-        <v>-2.457235191512501</v>
+        <v>-2.92084055081571</v>
       </c>
       <c r="G86">
-        <v>-1.623045759479122</v>
+        <v>-3.462384861098194</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-2.394284004587185</v>
       </c>
       <c r="E87">
-        <v>-19.49554911255128</v>
+        <v>-20.84235803869851</v>
       </c>
       <c r="F87">
-        <v>-2.518293389376354</v>
+        <v>-2.786739460572917</v>
       </c>
       <c r="G87">
-        <v>-2.106524451125365</v>
+        <v>-3.581951834340051</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-2.558022363853172</v>
       </c>
       <c r="E88">
-        <v>-21.87825552490112</v>
+        <v>-21.22555750922758</v>
       </c>
       <c r="F88">
-        <v>-2.567640873848489</v>
+        <v>-2.482315550242358</v>
       </c>
       <c r="G88">
-        <v>-1.656621312338411</v>
+        <v>-4.018632654243157</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-2.762054809059179</v>
       </c>
       <c r="E89">
-        <v>-24.22330314740318</v>
+        <v>-23.92514389026416</v>
       </c>
       <c r="F89">
-        <v>-2.651044370326235</v>
+        <v>-2.497404308351708</v>
       </c>
       <c r="G89">
-        <v>-1.445428370206145</v>
+        <v>-4.070071910832352</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-2.995092900527196</v>
       </c>
       <c r="E90">
-        <v>-24.37825847099764</v>
+        <v>-24.18956601604604</v>
       </c>
       <c r="F90">
-        <v>-2.340010071504631</v>
+        <v>-2.576805779981137</v>
       </c>
       <c r="G90">
-        <v>-1.155222637688093</v>
+        <v>-3.324513881569706</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-3.248584789967837</v>
       </c>
       <c r="E91">
-        <v>-28.09725869284891</v>
+        <v>-28.46178726504435</v>
       </c>
       <c r="F91">
-        <v>-2.390246014995328</v>
+        <v>-2.359065221079199</v>
       </c>
       <c r="G91">
-        <v>-1.813703387631289</v>
+        <v>-2.825902686263455</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-3.508634599131646</v>
       </c>
       <c r="E92">
-        <v>-28.80059863335023</v>
+        <v>-30.69497478684594</v>
       </c>
       <c r="F92">
-        <v>-2.310217395823384</v>
+        <v>-2.099483943744307</v>
       </c>
       <c r="G92">
-        <v>-1.359969947655398</v>
+        <v>-2.981038160779242</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-3.764977819590806</v>
       </c>
       <c r="E93">
-        <v>-31.90846317397035</v>
+        <v>-30.93593036032007</v>
       </c>
       <c r="F93">
-        <v>-2.153504152519947</v>
+        <v>-2.522034102748622</v>
       </c>
       <c r="G93">
-        <v>-1.18644439266896</v>
+        <v>-2.766955112391192</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-4.003701586702195</v>
       </c>
       <c r="E94">
-        <v>-34.08078121239784</v>
+        <v>-34.43748910998203</v>
       </c>
       <c r="F94">
-        <v>-2.487590082793729</v>
+        <v>-2.389465247979016</v>
       </c>
       <c r="G94">
-        <v>-2.322613690110213</v>
+        <v>-3.078894576374559</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-4.217326084282989</v>
       </c>
       <c r="E95">
-        <v>-36.65786784305293</v>
+        <v>-36.00629968164429</v>
       </c>
       <c r="F95">
-        <v>-2.452982149276589</v>
+        <v>-2.447671191489162</v>
       </c>
       <c r="G95">
-        <v>-2.153206453774628</v>
+        <v>-3.266688582635256</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-4.396626028564377</v>
       </c>
       <c r="E96">
-        <v>-38.51423198572824</v>
+        <v>-37.67979045846786</v>
       </c>
       <c r="F96">
-        <v>-2.160713973699985</v>
+        <v>-1.939813921496745</v>
       </c>
       <c r="G96">
-        <v>-2.144539445552816</v>
+        <v>-3.308954317535131</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-4.539088211630541</v>
       </c>
       <c r="E97">
-        <v>-40.79196157786928</v>
+        <v>-40.30253089983128</v>
       </c>
       <c r="F97">
-        <v>-2.334241422707643</v>
+        <v>-2.50197329991775</v>
       </c>
       <c r="G97">
-        <v>-2.704882383529857</v>
+        <v>-4.658379026979617</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-4.640822632528029</v>
       </c>
       <c r="E98">
-        <v>-43.08271053278236</v>
+        <v>-41.56239538926824</v>
       </c>
       <c r="F98">
-        <v>-2.282318040564046</v>
+        <v>-2.420094912236573</v>
       </c>
       <c r="G98">
-        <v>-2.258882377933704</v>
+        <v>-4.015520741436242</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.703921864448064</v>
       </c>
       <c r="E99">
-        <v>-45.96739602464546</v>
+        <v>-46.83726153983084</v>
       </c>
       <c r="F99">
-        <v>-2.281250622777039</v>
+        <v>-2.675743055930471</v>
       </c>
       <c r="G99">
-        <v>-3.320143961457868</v>
+        <v>-4.463848060546503</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-4.725574847755913</v>
       </c>
       <c r="E100">
-        <v>-48.9028208035275</v>
+        <v>-47.37613183284758</v>
       </c>
       <c r="F100">
-        <v>-2.471532096664131</v>
+        <v>-2.325118484781754</v>
       </c>
       <c r="G100">
-        <v>-3.89996945993352</v>
+        <v>-5.375860319523705</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-4.711514812324417</v>
       </c>
       <c r="E101">
-        <v>-50.32154982174605</v>
+        <v>-49.83139005939282</v>
       </c>
       <c r="F101">
-        <v>-2.124434438589098</v>
+        <v>-2.664656322669437</v>
       </c>
       <c r="G101">
-        <v>-4.045438141474635</v>
+        <v>-4.851317621008342</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-4.652608846210993</v>
       </c>
       <c r="E102">
-        <v>-52.05784826881901</v>
+        <v>-51.85606625974822</v>
       </c>
       <c r="F102">
-        <v>-2.523836360080392</v>
+        <v>-2.414059408992833</v>
       </c>
       <c r="G102">
-        <v>-4.053515872590457</v>
+        <v>-4.886465682998784</v>
       </c>
     </row>
   </sheetData>
